--- a/xls/square_high_un_16_tri3_24.xlsx
+++ b/xls/square_high_un_16_tri3_24.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>797</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>340</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>668</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>3738</v>
+      </c>
+      <c r="I22">
+        <v>-0.9883246905544004</v>
+      </c>
+      <c r="J22">
+        <v>-0.835461172622558</v>
+      </c>
+      <c r="K22">
+        <v>1.904838005576876</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>797</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>340</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>741</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>4164</v>
+      </c>
+      <c r="I23">
+        <v>-0.0012118679372723365</v>
+      </c>
+      <c r="J23">
+        <v>-0.0012714389677560545</v>
+      </c>
+      <c r="K23">
+        <v>2.971255481898057</v>
+      </c>
+    </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>11</v>
